--- a/S2 CP/ClinicalExam/CE_CP_ESMAC_T0_T1.xlsx
+++ b/S2 CP/ClinicalExam/CE_CP_ESMAC_T0_T1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GBW_MyPrograms\PredSim-workshop-ESMAC-2026\S2 CP\ClinicalExam\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GBW_MyPrograms\PredSim-workshop-ESMAC-2026_vsync\S2 CP\ClinicalExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A13660-0FE9-4BEB-A801-4DFF3214B047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B4042A-AAB3-43F1-9015-9EBF196849B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1152" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CE" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>pROM_Poplbi_L</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>CP_ESMAC</t>
-  </si>
-  <si>
-    <t>Step 2. Scaling muscle strength</t>
   </si>
   <si>
     <t>Step 3. Scaling muscle fiber length of the hamstrings</t>
@@ -649,7 +646,19 @@
     <t>white cell = to implement in model (in corresponding steps)</t>
   </si>
   <si>
-    <t xml:space="preserve">Step 6b. Adapt the knee extension deficit </t>
+    <t>I.2. Scaling muscle strength</t>
+  </si>
+  <si>
+    <t>I.3. Scaling muscle fiber length of the hamstrings</t>
+  </si>
+  <si>
+    <t>I.4. Scaling muscle fiber length of iliopsoas</t>
+  </si>
+  <si>
+    <t>I.5. Adjusting coordinate limit torques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II.2. Adapt the knee extension deficit </t>
   </si>
 </sst>
 </file>
@@ -919,7 +928,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -955,7 +964,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1308,25 +1316,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="33" t="s">
-        <v>35</v>
+      <c r="A1" s="32" t="s">
+        <v>34</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="10"/>
       <c r="D1" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1" s="12"/>
       <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="10"/>
       <c r="D2" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" s="12"/>
       <c r="F2" s="10"/>
@@ -1341,12 +1349,12 @@
     </row>
     <row r="4" spans="1:13" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="10"/>
-      <c r="B4" s="32" t="s">
-        <v>37</v>
+      <c r="B4" s="31" t="s">
+        <v>36</v>
       </c>
       <c r="C4" s="13"/>
-      <c r="D4" s="32" t="s">
-        <v>38</v>
+      <c r="D4" s="31" t="s">
+        <v>37</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
@@ -1355,40 +1363,39 @@
       <c r="A5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17" t="s">
-        <v>36</v>
+      <c r="B5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="18"/>
-      <c r="B6" s="27" t="s">
-        <v>28</v>
+      <c r="A6" s="17"/>
+      <c r="B6" s="26" t="s">
+        <v>62</v>
       </c>
       <c r="C6" s="13"/>
-      <c r="D6" s="24"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="12"/>
-      <c r="F6" s="19" t="s">
-        <v>31</v>
+      <c r="F6" s="18" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="24">
         <v>3</v>
       </c>
       <c r="C7" s="13"/>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <v>3</v>
       </c>
       <c r="E7" s="12"/>
-      <c r="F7" s="19" t="s">
-        <v>40</v>
+      <c r="F7" s="18" t="s">
+        <v>39</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="3"/>
@@ -1399,16 +1406,16 @@
       <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="24">
         <v>3</v>
       </c>
       <c r="C8" s="13"/>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>3</v>
       </c>
       <c r="E8" s="12"/>
-      <c r="F8" s="19" t="s">
-        <v>41</v>
+      <c r="F8" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="3"/>
@@ -1419,16 +1426,16 @@
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <v>5</v>
       </c>
       <c r="C9" s="13"/>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <v>5</v>
       </c>
       <c r="E9" s="12"/>
-      <c r="F9" s="19" t="s">
-        <v>42</v>
+      <c r="F9" s="18" t="s">
+        <v>41</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="3"/>
@@ -1439,16 +1446,16 @@
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="24">
         <v>5</v>
       </c>
       <c r="C10" s="13"/>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <v>5</v>
       </c>
       <c r="E10" s="12"/>
-      <c r="F10" s="19" t="s">
-        <v>43</v>
+      <c r="F10" s="18" t="s">
+        <v>42</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="3"/>
@@ -1459,16 +1466,16 @@
       <c r="A11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <v>3</v>
       </c>
       <c r="C11" s="13"/>
-      <c r="D11" s="25">
+      <c r="D11" s="24">
         <v>3</v>
       </c>
       <c r="E11" s="12"/>
-      <c r="F11" s="19" t="s">
-        <v>44</v>
+      <c r="F11" s="18" t="s">
+        <v>43</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="3"/>
@@ -1479,16 +1486,16 @@
       <c r="A12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <v>3</v>
       </c>
       <c r="C12" s="13"/>
-      <c r="D12" s="25">
+      <c r="D12" s="24">
         <v>3</v>
       </c>
       <c r="E12" s="12"/>
-      <c r="F12" s="19" t="s">
-        <v>45</v>
+      <c r="F12" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="3"/>
@@ -1499,16 +1506,16 @@
       <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <v>4</v>
       </c>
       <c r="C13" s="13"/>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <v>4</v>
       </c>
       <c r="E13" s="12"/>
-      <c r="F13" s="19" t="s">
-        <v>46</v>
+      <c r="F13" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="3"/>
@@ -1519,16 +1526,16 @@
       <c r="A14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <v>5</v>
       </c>
       <c r="C14" s="13"/>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <v>5</v>
       </c>
       <c r="E14" s="12"/>
-      <c r="F14" s="19" t="s">
-        <v>47</v>
+      <c r="F14" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="3"/>
@@ -1539,16 +1546,16 @@
       <c r="A15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="24">
         <v>3</v>
       </c>
       <c r="C15" s="13"/>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <v>3</v>
       </c>
       <c r="E15" s="12"/>
-      <c r="F15" s="19" t="s">
-        <v>48</v>
+      <c r="F15" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="3"/>
@@ -1559,16 +1566,16 @@
       <c r="A16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="24">
         <v>4</v>
       </c>
       <c r="C16" s="13"/>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <v>4</v>
       </c>
       <c r="E16" s="12"/>
-      <c r="F16" s="19" t="s">
-        <v>49</v>
+      <c r="F16" s="18" t="s">
+        <v>48</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="3"/>
@@ -1579,16 +1586,16 @@
       <c r="A17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="24">
         <v>3</v>
       </c>
       <c r="C17" s="13"/>
-      <c r="D17" s="25">
+      <c r="D17" s="24">
         <v>3</v>
       </c>
       <c r="E17" s="12"/>
-      <c r="F17" s="19" t="s">
-        <v>50</v>
+      <c r="F17" s="18" t="s">
+        <v>49</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="3"/>
@@ -1597,49 +1604,49 @@
       <c r="A18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="24">
         <v>3</v>
       </c>
       <c r="C18" s="13"/>
-      <c r="D18" s="25">
+      <c r="D18" s="24">
         <v>3</v>
       </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="19" t="s">
-        <v>51</v>
+      <c r="F18" s="18" t="s">
+        <v>50</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="3"/>
     </row>
     <row r="19" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A19" s="10"/>
-      <c r="B19" s="24"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="13"/>
-      <c r="D19" s="24"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="12"/>
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:16384" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="34"/>
+      <c r="B20" s="30"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="33"/>
     </row>
     <row r="21" spans="1:16384" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="18" t="s">
-        <v>29</v>
+      <c r="A21" s="17" t="s">
+        <v>28</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>29</v>
+      <c r="B21" s="26" t="s">
+        <v>63</v>
       </c>
       <c r="C21" s="13"/>
-      <c r="D21" s="24"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="19" t="s">
-        <v>32</v>
+      <c r="F21" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -18024,159 +18031,159 @@
       <c r="A22" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <v>-70</v>
       </c>
       <c r="C22" s="13"/>
-      <c r="D22" s="25">
+      <c r="D22" s="24">
         <v>-70</v>
       </c>
       <c r="E22" s="12"/>
-      <c r="F22" s="19" t="s">
-        <v>52</v>
+      <c r="F22" s="18" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="27">
         <v>-65</v>
       </c>
       <c r="C23" s="13"/>
-      <c r="D23" s="25">
+      <c r="D23" s="24">
         <v>-65</v>
       </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="19" t="s">
-        <v>53</v>
+      <c r="F23" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="24">
         <v>15</v>
       </c>
       <c r="C24" s="13"/>
-      <c r="D24" s="25">
+      <c r="D24" s="24">
         <v>15</v>
       </c>
       <c r="E24" s="12"/>
-      <c r="F24" s="19" t="s">
-        <v>54</v>
+      <c r="F24" s="18" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="24">
         <v>10</v>
       </c>
       <c r="C25" s="13"/>
-      <c r="D25" s="25">
+      <c r="D25" s="24">
         <v>10</v>
       </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="19" t="s">
-        <v>55</v>
+      <c r="F25" s="18" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="24">
         <v>30</v>
       </c>
       <c r="C26" s="13"/>
-      <c r="D26" s="25">
+      <c r="D26" s="24">
         <v>30</v>
       </c>
       <c r="E26" s="12"/>
-      <c r="F26" s="19" t="s">
-        <v>56</v>
+      <c r="F26" s="18" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="24">
         <v>30</v>
       </c>
       <c r="C27" s="13"/>
-      <c r="D27" s="25">
+      <c r="D27" s="24">
         <v>30</v>
       </c>
       <c r="E27" s="12"/>
-      <c r="F27" s="19" t="s">
-        <v>57</v>
+      <c r="F27" s="18" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A28" s="18" t="s">
-        <v>30</v>
+      <c r="A28" s="17" t="s">
+        <v>29</v>
       </c>
-      <c r="B28" s="27" t="s">
-        <v>30</v>
+      <c r="B28" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="C28" s="13"/>
-      <c r="D28" s="24"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="19" t="s">
-        <v>32</v>
+      <c r="F28" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>-80</v>
       </c>
       <c r="C29" s="13"/>
-      <c r="D29" s="25">
+      <c r="D29" s="24">
         <v>-80</v>
       </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="20" t="s">
-        <v>42</v>
+      <c r="F29" s="19" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="27">
         <v>-65</v>
       </c>
       <c r="C30" s="13"/>
-      <c r="D30" s="25">
+      <c r="D30" s="24">
         <v>-65</v>
       </c>
       <c r="E30" s="12"/>
-      <c r="F30" s="20" t="s">
-        <v>43</v>
+      <c r="F30" s="19" t="s">
+        <v>42</v>
       </c>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:16384" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="18" t="s">
-        <v>34</v>
+      <c r="A31" s="17" t="s">
+        <v>33</v>
       </c>
-      <c r="B31" s="27" t="s">
-        <v>34</v>
+      <c r="B31" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="C31" s="13"/>
-      <c r="D31" s="27" t="s">
-        <v>63</v>
+      <c r="D31" s="26" t="s">
+        <v>66</v>
       </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="20" t="s">
-        <v>33</v>
+      <c r="F31" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="H31" s="3"/>
     </row>
@@ -18184,16 +18191,16 @@
       <c r="A32" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <v>-10</v>
       </c>
       <c r="C32" s="13"/>
-      <c r="D32" s="28">
+      <c r="D32" s="27">
         <v>0</v>
       </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="20" t="s">
-        <v>58</v>
+      <c r="F32" s="19" t="s">
+        <v>57</v>
       </c>
       <c r="H32" s="3"/>
     </row>
@@ -18201,16 +18208,16 @@
       <c r="A33" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>-10</v>
       </c>
       <c r="C33" s="13"/>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <v>0</v>
       </c>
       <c r="E33" s="12"/>
-      <c r="F33" s="21" t="s">
-        <v>59</v>
+      <c r="F33" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="H33" s="3"/>
     </row>
@@ -18218,16 +18225,16 @@
       <c r="A34" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="28" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="13"/>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="28" t="s">
         <v>21</v>
       </c>
       <c r="E34" s="12"/>
-      <c r="F34" s="20" t="s">
-        <v>60</v>
+      <c r="F34" s="19" t="s">
+        <v>59</v>
       </c>
       <c r="H34" s="3"/>
     </row>
@@ -18235,16 +18242,16 @@
       <c r="A35" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="29" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="13"/>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="29" t="s">
         <v>21</v>
       </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="22" t="s">
-        <v>61</v>
+      <c r="F35" s="21" t="s">
+        <v>60</v>
       </c>
       <c r="H35" s="3"/>
     </row>

--- a/S2 CP/ClinicalExam/CE_CP_ESMAC_T0_T1.xlsx
+++ b/S2 CP/ClinicalExam/CE_CP_ESMAC_T0_T1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GBW_MyPrograms\PredSim-workshop-ESMAC-2026_vsync\S2 CP\ClinicalExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B4042A-AAB3-43F1-9015-9EBF196849B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC98C120-9EF0-4AB9-A2DF-ADF06E8273E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="67">
   <si>
     <t>pROM_Poplbi_L</t>
   </si>
@@ -646,19 +646,19 @@
     <t>white cell = to implement in model (in corresponding steps)</t>
   </si>
   <si>
-    <t>I.2. Scaling muscle strength</t>
+    <t>I.2 Step 5. Adjusting coordinate limit torques</t>
   </si>
   <si>
-    <t>I.3. Scaling muscle fiber length of the hamstrings</t>
+    <t>I.1 Step 2. Scaling muscle strength</t>
   </si>
   <si>
-    <t>I.4. Scaling muscle fiber length of iliopsoas</t>
+    <t>I.2 Step 4. Scaling muscle fiber length of iliopsoas</t>
   </si>
   <si>
-    <t>I.5. Adjusting coordinate limit torques</t>
+    <t>I.2 Step 3. Scaling muscle fiber length of the hamstrings</t>
   </si>
   <si>
-    <t xml:space="preserve">II.2. Adapt the knee extension deficit </t>
+    <t xml:space="preserve">II. Step 2. Adapt the knee extension deficit </t>
   </si>
 </sst>
 </file>
@@ -1301,11 +1301,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFD50"/>
+  <dimension ref="A1:XFD52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47.5546875" customWidth="1"/>
-    <col min="2" max="2" width="74.88671875" customWidth="1"/>
+    <col min="2" max="2" width="79.77734375" customWidth="1"/>
     <col min="3" max="3" width="2.77734375" customWidth="1"/>
     <col min="4" max="4" width="76.109375" customWidth="1"/>
     <col min="5" max="5" width="3.77734375" style="6" customWidth="1"/>
@@ -1373,7 +1373,7 @@
     <row r="6" spans="1:13" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="17"/>
       <c r="B6" s="26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="23"/>
@@ -1640,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="23"/>
@@ -18139,131 +18139,149 @@
     </row>
     <row r="29" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B29" s="27">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="24">
+        <v>-70</v>
+      </c>
+      <c r="E29" s="12"/>
+    </row>
+    <row r="30" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="27">
         <v>-80</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="19" t="s">
+      <c r="C30" s="13"/>
+      <c r="D30" s="24">
+        <v>-80</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="F30" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A30" s="7" t="s">
-        <v>4</v>
+    <row r="31" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A31" s="7" t="s">
+        <v>0</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B31" s="27">
         <v>-65</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="24">
+      <c r="C31" s="13"/>
+      <c r="D31" s="24">
         <v>-65</v>
       </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:16384" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="26" t="s">
-        <v>66</v>
-      </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:16384" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B32" s="27">
-        <v>-10</v>
+        <v>-65</v>
       </c>
       <c r="C32" s="13"/>
-      <c r="D32" s="27">
-        <v>0</v>
+      <c r="D32" s="24">
+        <v>-65</v>
       </c>
       <c r="E32" s="12"/>
       <c r="F32" s="19" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A33" s="7" t="s">
-        <v>5</v>
+    <row r="33" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="17" t="s">
+        <v>33</v>
       </c>
-      <c r="B33" s="27">
-        <v>-10</v>
+      <c r="B33" s="26" t="s">
+        <v>62</v>
       </c>
       <c r="C33" s="13"/>
-      <c r="D33" s="27">
-        <v>0</v>
+      <c r="D33" s="26" t="s">
+        <v>66</v>
       </c>
       <c r="E33" s="12"/>
-      <c r="F33" s="20" t="s">
-        <v>58</v>
+      <c r="F33" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
-      <c r="B34" s="28" t="s">
-        <v>21</v>
+      <c r="B34" s="27">
+        <v>-10</v>
       </c>
       <c r="C34" s="13"/>
-      <c r="D34" s="28" t="s">
-        <v>21</v>
+      <c r="D34" s="27">
+        <v>0</v>
       </c>
       <c r="E34" s="12"/>
       <c r="F34" s="19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
-      <c r="B35" s="29" t="s">
-        <v>21</v>
+      <c r="B35" s="27">
+        <v>-10</v>
       </c>
       <c r="C35" s="13"/>
-      <c r="D35" s="29" t="s">
-        <v>21</v>
+      <c r="D35" s="27">
+        <v>0</v>
       </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="21" t="s">
-        <v>60</v>
+      <c r="F35" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A36" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="F36" s="19" t="s">
+        <v>59</v>
+      </c>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G37" s="1"/>
+    <row r="37" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G38" s="1"/>
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -18276,11 +18294,11 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G41" s="1"/>
-      <c r="H41" s="4"/>
+      <c r="H41" s="3"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G42" s="1"/>
-      <c r="H42" s="4"/>
+      <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G43" s="1"/>
@@ -18314,6 +18332,14 @@
       <c r="G50" s="1"/>
       <c r="H50" s="4"/>
     </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G51" s="1"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G52" s="1"/>
+      <c r="H52" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
